--- a/artfynd/A 28033-2023 artfynd.xlsx
+++ b/artfynd/A 28033-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ89"/>
+  <dimension ref="A1:AZ100"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3631,10 +3631,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>112820900</v>
+        <v>137489475</v>
       </c>
       <c r="B24" t="n">
-        <v>106813</v>
+        <v>43487</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3642,38 +3642,44 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>7</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>503297</v>
+        <v>503387</v>
       </c>
       <c r="R24" t="n">
-        <v>6610235</v>
+        <v>6610199</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3700,17 +3706,12 @@
       </c>
       <c r="Y24" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>2 till 4 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3721,11 +3722,26 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ24" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK24" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO24" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
@@ -3733,19 +3749,23 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY24" t="inlineStr"/>
+      <c r="AY24" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ24" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820900</t>
+          <t>https://artportalen.se/Sighting/137489475</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>112820901</v>
+        <v>137489476</v>
       </c>
       <c r="B25" t="n">
-        <v>106813</v>
+        <v>43487</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3753,21 +3773,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -3775,16 +3795,22 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>503299</v>
+        <v>503385</v>
       </c>
       <c r="R25" t="n">
-        <v>6610247</v>
+        <v>6610201</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3811,17 +3837,12 @@
       </c>
       <c r="Y25" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Träd 2 dm dbh. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3832,11 +3853,26 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO25" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
@@ -3844,19 +3880,23 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY25" t="inlineStr"/>
+      <c r="AY25" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ25" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820901</t>
+          <t>https://artportalen.se/Sighting/137489476</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>112820903</v>
+        <v>137489477</v>
       </c>
       <c r="B26" t="n">
-        <v>106813</v>
+        <v>43487</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3864,38 +3904,44 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>503304</v>
+        <v>503384</v>
       </c>
       <c r="R26" t="n">
-        <v>6610248</v>
+        <v>6610199</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3922,17 +3968,12 @@
       </c>
       <c r="Y26" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>2 till 5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3943,11 +3984,26 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ26" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK26" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO26" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
@@ -3955,19 +4011,23 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY26" t="inlineStr"/>
+      <c r="AY26" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ26" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820903</t>
+          <t>https://artportalen.se/Sighting/137489477</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>112820904</v>
+        <v>137489478</v>
       </c>
       <c r="B27" t="n">
-        <v>106813</v>
+        <v>43487</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3975,38 +4035,44 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>503302</v>
+        <v>503384</v>
       </c>
       <c r="R27" t="n">
-        <v>6610265</v>
+        <v>6610198</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -4033,17 +4099,12 @@
       </c>
       <c r="Y27" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC27" t="inlineStr">
-        <is>
-          <t>1 dm dbh och ca 8 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -4054,11 +4115,26 @@
       </c>
       <c r="AG27" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ27" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK27" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO27" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
@@ -4066,19 +4142,23 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY27" t="inlineStr"/>
+      <c r="AY27" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ27" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820904</t>
+          <t>https://artportalen.se/Sighting/137489478</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>112820905</v>
+        <v>137489479</v>
       </c>
       <c r="B28" t="n">
-        <v>106813</v>
+        <v>43487</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -4086,38 +4166,44 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>6</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>503303</v>
+        <v>503384</v>
       </c>
       <c r="R28" t="n">
-        <v>6610262</v>
+        <v>6610202</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -4144,17 +4230,12 @@
       </c>
       <c r="Y28" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>1 till 3 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -4165,11 +4246,26 @@
       </c>
       <c r="AG28" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ28" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK28" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO28" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
@@ -4177,19 +4273,23 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY28" t="inlineStr"/>
+      <c r="AY28" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ28" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820905</t>
+          <t>https://artportalen.se/Sighting/137489479</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>112820907</v>
+        <v>137489500</v>
       </c>
       <c r="B29" t="n">
-        <v>106813</v>
+        <v>43487</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -4197,38 +4297,44 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>503295</v>
+        <v>503403</v>
       </c>
       <c r="R29" t="n">
-        <v>6610262</v>
+        <v>6610184</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -4255,17 +4361,12 @@
       </c>
       <c r="Y29" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Under 0.5 m höga plantor. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -4276,31 +4377,50 @@
       </c>
       <c r="AG29" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ29" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK29" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO29" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY29" t="inlineStr"/>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ29" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820907</t>
+          <t>https://artportalen.se/Sighting/137489500</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>112820908</v>
+        <v>137489501</v>
       </c>
       <c r="B30" t="n">
-        <v>106813</v>
+        <v>43487</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -4308,38 +4428,44 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>503294</v>
+        <v>503381</v>
       </c>
       <c r="R30" t="n">
-        <v>6610265</v>
+        <v>6610184</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -4366,17 +4492,12 @@
       </c>
       <c r="Y30" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>8 m hög. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -4387,31 +4508,50 @@
       </c>
       <c r="AG30" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ30" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK30" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO30" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY30" t="inlineStr"/>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ30" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820908</t>
+          <t>https://artportalen.se/Sighting/137489501</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>112820909</v>
+        <v>137489503</v>
       </c>
       <c r="B31" t="n">
-        <v>106813</v>
+        <v>43487</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -4419,38 +4559,44 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>503278</v>
+        <v>503382</v>
       </c>
       <c r="R31" t="n">
-        <v>6610268</v>
+        <v>6610185</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4477,17 +4623,12 @@
       </c>
       <c r="Y31" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -4498,31 +4639,50 @@
       </c>
       <c r="AG31" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ31" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK31" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO31" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY31" t="inlineStr"/>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ31" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820909</t>
+          <t>https://artportalen.se/Sighting/137489503</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>112820910</v>
+        <v>137489504</v>
       </c>
       <c r="B32" t="n">
-        <v>106813</v>
+        <v>43487</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -4530,38 +4690,44 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>2</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>503278</v>
+        <v>503376</v>
       </c>
       <c r="R32" t="n">
-        <v>6610274</v>
+        <v>6610190</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4588,17 +4754,12 @@
       </c>
       <c r="Y32" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>4 till 8 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -4609,31 +4770,50 @@
       </c>
       <c r="AG32" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ32" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK32" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO32" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY32" t="inlineStr"/>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ32" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820910</t>
+          <t>https://artportalen.se/Sighting/137489504</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>112820912</v>
+        <v>137489505</v>
       </c>
       <c r="B33" t="n">
-        <v>106813</v>
+        <v>43487</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4641,38 +4821,44 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>500</t>
-        </is>
-      </c>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:17 Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>503254</v>
+        <v>503334</v>
       </c>
       <c r="R33" t="n">
-        <v>6610261</v>
+        <v>6610233</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4699,17 +4885,12 @@
       </c>
       <c r="Y33" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4720,31 +4901,50 @@
       </c>
       <c r="AG33" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ33" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK33" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO33" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
-        </is>
-      </c>
-      <c r="AY33" t="inlineStr"/>
+          <t>Inger Holst</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ33" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820912</t>
+          <t>https://artportalen.se/Sighting/137489505</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>112820913</v>
+        <v>137489863</v>
       </c>
       <c r="B34" t="n">
-        <v>106813</v>
+        <v>43487</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4752,38 +4952,44 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220785</v>
+        <v>100943</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Asknätfjäril</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Euphydryas maturna</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>kolonier</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>400 m SV Ömanstorp, Vstm</t>
+          <t>Natorpsområdet Yta 7:3 Ömansttorp, Vstm</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>503253</v>
+        <v>503304</v>
       </c>
       <c r="R34" t="n">
-        <v>6610273</v>
+        <v>6610262</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4810,17 +5016,12 @@
       </c>
       <c r="Y34" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AA34" t="inlineStr">
         <is>
-          <t>2023-07-18</t>
-        </is>
-      </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>3 till 7 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2026-08-13</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4831,11 +5032,26 @@
       </c>
       <c r="AG34" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ34" t="inlineStr">
+        <is>
+          <t>ask</t>
+        </is>
+      </c>
+      <c r="AK34" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="AO34" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
       </c>
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Jesper Hansson</t>
+          <t>Henrik Josefsson</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
@@ -4843,16 +5059,20 @@
           <t>Jesper Hansson</t>
         </is>
       </c>
-      <c r="AY34" t="inlineStr"/>
+      <c r="AY34" t="inlineStr">
+        <is>
+          <t>Biogeografisk uppföljning av fjärilar</t>
+        </is>
+      </c>
       <c r="AZ34" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820913</t>
+          <t>https://artportalen.se/Sighting/137489863</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>112820914</v>
+        <v>112820900</v>
       </c>
       <c r="B35" t="n">
         <v>106813</v>
@@ -4891,10 +5111,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>503236</v>
+        <v>503297</v>
       </c>
       <c r="R35" t="n">
-        <v>6610265</v>
+        <v>6610235</v>
       </c>
       <c r="S35" t="n">
         <v>10</v>
@@ -4931,7 +5151,7 @@
       </c>
       <c r="AC35" t="inlineStr">
         <is>
-          <t>Över 15 m höga. 15 till 30 cm dbh. Minst tre med askskottsjuka. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2 till 4 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4957,13 +5177,13 @@
       <c r="AY35" t="inlineStr"/>
       <c r="AZ35" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820914</t>
+          <t>https://artportalen.se/Sighting/112820900</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>112820915</v>
+        <v>112820901</v>
       </c>
       <c r="B36" t="n">
         <v>106813</v>
@@ -4993,7 +5213,7 @@
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>300</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P36" t="inlineStr">
@@ -5002,10 +5222,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>503240</v>
+        <v>503299</v>
       </c>
       <c r="R36" t="n">
-        <v>6610256</v>
+        <v>6610247</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -5042,7 +5262,7 @@
       </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Träd 2 dm dbh. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -5068,13 +5288,13 @@
       <c r="AY36" t="inlineStr"/>
       <c r="AZ36" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820915</t>
+          <t>https://artportalen.se/Sighting/112820901</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>112820916</v>
+        <v>112820903</v>
       </c>
       <c r="B37" t="n">
         <v>106813</v>
@@ -5113,10 +5333,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>503260</v>
+        <v>503304</v>
       </c>
       <c r="R37" t="n">
-        <v>6610237</v>
+        <v>6610248</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -5153,7 +5373,7 @@
       </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Från 2 till 7 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>2 till 5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -5179,13 +5399,13 @@
       <c r="AY37" t="inlineStr"/>
       <c r="AZ37" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820916</t>
+          <t>https://artportalen.se/Sighting/112820903</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>112820917</v>
+        <v>112820904</v>
       </c>
       <c r="B38" t="n">
         <v>106813</v>
@@ -5215,7 +5435,7 @@
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P38" t="inlineStr">
@@ -5224,10 +5444,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>503266</v>
+        <v>503302</v>
       </c>
       <c r="R38" t="n">
-        <v>6610239</v>
+        <v>6610265</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5264,7 +5484,7 @@
       </c>
       <c r="AC38" t="inlineStr">
         <is>
-          <t>Träd med tre stammar med vardera ca 2 dm dbh. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>1 dm dbh och ca 8 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -5290,13 +5510,13 @@
       <c r="AY38" t="inlineStr"/>
       <c r="AZ38" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820917</t>
+          <t>https://artportalen.se/Sighting/112820904</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>112820918</v>
+        <v>112820905</v>
       </c>
       <c r="B39" t="n">
         <v>106813</v>
@@ -5326,7 +5546,7 @@
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>6</t>
         </is>
       </c>
       <c r="P39" t="inlineStr">
@@ -5335,10 +5555,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>503247</v>
+        <v>503303</v>
       </c>
       <c r="R39" t="n">
-        <v>6610235</v>
+        <v>6610262</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -5375,7 +5595,7 @@
       </c>
       <c r="AC39" t="inlineStr">
         <is>
-          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>1 till 3 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -5401,13 +5621,13 @@
       <c r="AY39" t="inlineStr"/>
       <c r="AZ39" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820918</t>
+          <t>https://artportalen.se/Sighting/112820905</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>112820919</v>
+        <v>112820907</v>
       </c>
       <c r="B40" t="n">
         <v>106813</v>
@@ -5437,7 +5657,7 @@
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P40" t="inlineStr">
@@ -5446,10 +5666,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>503232</v>
+        <v>503295</v>
       </c>
       <c r="R40" t="n">
-        <v>6610241</v>
+        <v>6610262</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -5486,7 +5706,7 @@
       </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Från 1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Under 0.5 m höga plantor. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -5512,13 +5732,13 @@
       <c r="AY40" t="inlineStr"/>
       <c r="AZ40" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820919</t>
+          <t>https://artportalen.se/Sighting/112820907</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>112820920</v>
+        <v>112820908</v>
       </c>
       <c r="B41" t="n">
         <v>106813</v>
@@ -5548,7 +5768,7 @@
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P41" t="inlineStr">
@@ -5557,7 +5777,7 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>503224</v>
+        <v>503294</v>
       </c>
       <c r="R41" t="n">
         <v>6610265</v>
@@ -5597,7 +5817,7 @@
       </c>
       <c r="AC41" t="inlineStr">
         <is>
-          <t>Från 1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>8 m hög. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5623,13 +5843,13 @@
       <c r="AY41" t="inlineStr"/>
       <c r="AZ41" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820920</t>
+          <t>https://artportalen.se/Sighting/112820908</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>112820924</v>
+        <v>112820909</v>
       </c>
       <c r="B42" t="n">
         <v>106813</v>
@@ -5659,7 +5879,7 @@
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5668,10 +5888,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>503237</v>
+        <v>503278</v>
       </c>
       <c r="R42" t="n">
-        <v>6610228</v>
+        <v>6610268</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -5708,7 +5928,7 @@
       </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5734,13 +5954,13 @@
       <c r="AY42" t="inlineStr"/>
       <c r="AZ42" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820924</t>
+          <t>https://artportalen.se/Sighting/112820909</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>112820925</v>
+        <v>112820910</v>
       </c>
       <c r="B43" t="n">
         <v>106813</v>
@@ -5770,7 +5990,7 @@
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5779,10 +5999,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>503243</v>
+        <v>503278</v>
       </c>
       <c r="R43" t="n">
-        <v>6610208</v>
+        <v>6610274</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5819,7 +6039,7 @@
       </c>
       <c r="AC43" t="inlineStr">
         <is>
-          <t>Från 0.1 till 1 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>4 till 8 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5845,13 +6065,13 @@
       <c r="AY43" t="inlineStr"/>
       <c r="AZ43" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820925</t>
+          <t>https://artportalen.se/Sighting/112820910</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>112820926</v>
+        <v>112820912</v>
       </c>
       <c r="B44" t="n">
         <v>106813</v>
@@ -5881,7 +6101,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>500</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5890,10 +6110,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>503229</v>
+        <v>503254</v>
       </c>
       <c r="R44" t="n">
-        <v>6610215</v>
+        <v>6610261</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5930,7 +6150,7 @@
       </c>
       <c r="AC44" t="inlineStr">
         <is>
-          <t>Ca 4 dm dbh. Över 15 m hög. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5956,13 +6176,13 @@
       <c r="AY44" t="inlineStr"/>
       <c r="AZ44" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820926</t>
+          <t>https://artportalen.se/Sighting/112820912</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>112820930</v>
+        <v>112820913</v>
       </c>
       <c r="B45" t="n">
         <v>106813</v>
@@ -5992,7 +6212,7 @@
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>20</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P45" t="inlineStr">
@@ -6001,10 +6221,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>503256</v>
+        <v>503253</v>
       </c>
       <c r="R45" t="n">
-        <v>6610210</v>
+        <v>6610273</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -6041,7 +6261,7 @@
       </c>
       <c r="AC45" t="inlineStr">
         <is>
-          <t>Från 0.1 till 1 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>3 till 7 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -6067,13 +6287,13 @@
       <c r="AY45" t="inlineStr"/>
       <c r="AZ45" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820930</t>
+          <t>https://artportalen.se/Sighting/112820913</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>112820931</v>
+        <v>112820914</v>
       </c>
       <c r="B46" t="n">
         <v>106813</v>
@@ -6103,7 +6323,7 @@
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>200</t>
+          <t>7</t>
         </is>
       </c>
       <c r="P46" t="inlineStr">
@@ -6112,10 +6332,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>503266</v>
+        <v>503236</v>
       </c>
       <c r="R46" t="n">
-        <v>6610214</v>
+        <v>6610265</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -6152,7 +6372,7 @@
       </c>
       <c r="AC46" t="inlineStr">
         <is>
-          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Över 15 m höga. 15 till 30 cm dbh. Minst tre med askskottsjuka. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -6178,13 +6398,13 @@
       <c r="AY46" t="inlineStr"/>
       <c r="AZ46" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820931</t>
+          <t>https://artportalen.se/Sighting/112820914</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>112820932</v>
+        <v>112820915</v>
       </c>
       <c r="B47" t="n">
         <v>106813</v>
@@ -6214,7 +6434,7 @@
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>300</t>
         </is>
       </c>
       <c r="P47" t="inlineStr">
@@ -6223,10 +6443,10 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>503277</v>
+        <v>503240</v>
       </c>
       <c r="R47" t="n">
-        <v>6610236</v>
+        <v>6610256</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -6263,7 +6483,7 @@
       </c>
       <c r="AC47" t="inlineStr">
         <is>
-          <t>Kring 5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -6289,13 +6509,13 @@
       <c r="AY47" t="inlineStr"/>
       <c r="AZ47" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820932</t>
+          <t>https://artportalen.se/Sighting/112820915</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>112820933</v>
+        <v>112820916</v>
       </c>
       <c r="B48" t="n">
         <v>106813</v>
@@ -6325,7 +6545,7 @@
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>15</t>
         </is>
       </c>
       <c r="P48" t="inlineStr">
@@ -6334,10 +6554,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>503276</v>
+        <v>503260</v>
       </c>
       <c r="R48" t="n">
-        <v>6610240</v>
+        <v>6610237</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -6374,7 +6594,7 @@
       </c>
       <c r="AC48" t="inlineStr">
         <is>
-          <t>Från 1 till 3 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 2 till 7 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -6400,13 +6620,13 @@
       <c r="AY48" t="inlineStr"/>
       <c r="AZ48" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820933</t>
+          <t>https://artportalen.se/Sighting/112820916</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>112820944</v>
+        <v>112820917</v>
       </c>
       <c r="B49" t="n">
         <v>106813</v>
@@ -6436,7 +6656,7 @@
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P49" t="inlineStr">
@@ -6445,10 +6665,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>503357</v>
+        <v>503266</v>
       </c>
       <c r="R49" t="n">
-        <v>6610187</v>
+        <v>6610239</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -6485,7 +6705,7 @@
       </c>
       <c r="AC49" t="inlineStr">
         <is>
-          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Träd med tre stammar med vardera ca 2 dm dbh. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -6511,13 +6731,13 @@
       <c r="AY49" t="inlineStr"/>
       <c r="AZ49" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820944</t>
+          <t>https://artportalen.se/Sighting/112820917</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>112820950</v>
+        <v>112820918</v>
       </c>
       <c r="B50" t="n">
         <v>106813</v>
@@ -6547,7 +6767,7 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P50" t="inlineStr">
@@ -6556,10 +6776,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>503370</v>
+        <v>503247</v>
       </c>
       <c r="R50" t="n">
-        <v>6610173</v>
+        <v>6610235</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6596,7 +6816,7 @@
       </c>
       <c r="AC50" t="inlineStr">
         <is>
-          <t>Från 0.1 till 0.5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -6622,13 +6842,13 @@
       <c r="AY50" t="inlineStr"/>
       <c r="AZ50" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820950</t>
+          <t>https://artportalen.se/Sighting/112820918</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>112820952</v>
+        <v>112820919</v>
       </c>
       <c r="B51" t="n">
         <v>106813</v>
@@ -6658,7 +6878,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P51" t="inlineStr">
@@ -6667,10 +6887,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>503371</v>
+        <v>503232</v>
       </c>
       <c r="R51" t="n">
-        <v>6610163</v>
+        <v>6610241</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6707,7 +6927,7 @@
       </c>
       <c r="AC51" t="inlineStr">
         <is>
-          <t>Ca 15 till 30 cm dbh och över 10 m höga. Med askskottsjuka men levande. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -6733,13 +6953,13 @@
       <c r="AY51" t="inlineStr"/>
       <c r="AZ51" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820952</t>
+          <t>https://artportalen.se/Sighting/112820919</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>112820953</v>
+        <v>112820920</v>
       </c>
       <c r="B52" t="n">
         <v>106813</v>
@@ -6769,7 +6989,7 @@
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>25</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P52" t="inlineStr">
@@ -6778,10 +6998,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>503365</v>
+        <v>503224</v>
       </c>
       <c r="R52" t="n">
-        <v>6610155</v>
+        <v>6610265</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6818,7 +7038,7 @@
       </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Från 0.3 till 1 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6844,13 +7064,13 @@
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820953</t>
+          <t>https://artportalen.se/Sighting/112820920</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>112820954</v>
+        <v>112820924</v>
       </c>
       <c r="B53" t="n">
         <v>106813</v>
@@ -6880,7 +7100,7 @@
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P53" t="inlineStr">
@@ -6889,10 +7109,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>503343</v>
+        <v>503237</v>
       </c>
       <c r="R53" t="n">
-        <v>6610144</v>
+        <v>6610228</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6929,7 +7149,7 @@
       </c>
       <c r="AC53" t="inlineStr">
         <is>
-          <t>Ca 10 till 20 cm dbh och över 10 m höga. Ganska friska fortfarande. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6955,13 +7175,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820954</t>
+          <t>https://artportalen.se/Sighting/112820924</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>112820957</v>
+        <v>112820925</v>
       </c>
       <c r="B54" t="n">
         <v>106813</v>
@@ -6991,7 +7211,7 @@
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -7000,10 +7220,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>503313</v>
+        <v>503243</v>
       </c>
       <c r="R54" t="n">
-        <v>6610137</v>
+        <v>6610208</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -7040,7 +7260,7 @@
       </c>
       <c r="AC54" t="inlineStr">
         <is>
-          <t>Ca 4 m hög. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 1 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -7066,13 +7286,13 @@
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820957</t>
+          <t>https://artportalen.se/Sighting/112820925</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>112820958</v>
+        <v>112820926</v>
       </c>
       <c r="B55" t="n">
         <v>106813</v>
@@ -7102,7 +7322,7 @@
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P55" t="inlineStr">
@@ -7111,10 +7331,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>503298</v>
+        <v>503229</v>
       </c>
       <c r="R55" t="n">
-        <v>6610146</v>
+        <v>6610215</v>
       </c>
       <c r="S55" t="n">
         <v>10</v>
@@ -7151,7 +7371,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Från 0.1 till 0.5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Ca 4 dm dbh. Över 15 m hög. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -7177,13 +7397,13 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820958</t>
+          <t>https://artportalen.se/Sighting/112820926</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>112820964</v>
+        <v>112820930</v>
       </c>
       <c r="B56" t="n">
         <v>106813</v>
@@ -7213,7 +7433,7 @@
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>20</t>
         </is>
       </c>
       <c r="P56" t="inlineStr">
@@ -7222,10 +7442,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>503285</v>
+        <v>503256</v>
       </c>
       <c r="R56" t="n">
-        <v>6610146</v>
+        <v>6610210</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -7262,7 +7482,7 @@
       </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>Från ca 8 till 30 cm dbh och från ca 15 till 20 m höga. Några döende av askskottsjuka andra tillsynes helt friska. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 1 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -7288,13 +7508,13 @@
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820964</t>
+          <t>https://artportalen.se/Sighting/112820930</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>112820965</v>
+        <v>112820931</v>
       </c>
       <c r="B57" t="n">
         <v>106813</v>
@@ -7324,7 +7544,7 @@
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>200</t>
         </is>
       </c>
       <c r="P57" t="inlineStr">
@@ -7333,10 +7553,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>503282</v>
+        <v>503266</v>
       </c>
       <c r="R57" t="n">
-        <v>6610142</v>
+        <v>6610214</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -7373,7 +7593,7 @@
       </c>
       <c r="AC57" t="inlineStr">
         <is>
-          <t>Från 0.1 till 0.5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -7399,13 +7619,13 @@
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820965</t>
+          <t>https://artportalen.se/Sighting/112820931</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>112820967</v>
+        <v>112820932</v>
       </c>
       <c r="B58" t="n">
         <v>106813</v>
@@ -7435,7 +7655,7 @@
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P58" t="inlineStr">
@@ -7444,10 +7664,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>503280</v>
+        <v>503277</v>
       </c>
       <c r="R58" t="n">
-        <v>6610159</v>
+        <v>6610236</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -7484,7 +7704,7 @@
       </c>
       <c r="AC58" t="inlineStr">
         <is>
-          <t>Ca 5 dm dbh. Ca 20 m hög. Spår av askskottsjuka. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Kring 5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -7510,13 +7730,13 @@
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820967</t>
+          <t>https://artportalen.se/Sighting/112820932</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>112820969</v>
+        <v>112820933</v>
       </c>
       <c r="B59" t="n">
         <v>106813</v>
@@ -7546,7 +7766,7 @@
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P59" t="inlineStr">
@@ -7555,10 +7775,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>503262</v>
+        <v>503276</v>
       </c>
       <c r="R59" t="n">
-        <v>6610165</v>
+        <v>6610240</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7595,7 +7815,7 @@
       </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Från 0.1 till 0.5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 1 till 3 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7621,13 +7841,13 @@
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820969</t>
+          <t>https://artportalen.se/Sighting/112820933</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>112820975</v>
+        <v>112820944</v>
       </c>
       <c r="B60" t="n">
         <v>106813</v>
@@ -7657,7 +7877,7 @@
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
@@ -7666,10 +7886,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>503254</v>
+        <v>503357</v>
       </c>
       <c r="R60" t="n">
-        <v>6610139</v>
+        <v>6610187</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7706,7 +7926,7 @@
       </c>
       <c r="AC60" t="inlineStr">
         <is>
-          <t>Från 0.1 till 0.5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 2 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7732,13 +7952,13 @@
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820975</t>
+          <t>https://artportalen.se/Sighting/112820944</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>112820979</v>
+        <v>112820950</v>
       </c>
       <c r="B61" t="n">
         <v>106813</v>
@@ -7768,7 +7988,7 @@
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P61" t="inlineStr">
@@ -7777,10 +7997,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>503243</v>
+        <v>503370</v>
       </c>
       <c r="R61" t="n">
-        <v>6610159</v>
+        <v>6610173</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7843,13 +8063,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820979</t>
+          <t>https://artportalen.se/Sighting/112820950</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>112820980</v>
+        <v>112820952</v>
       </c>
       <c r="B62" t="n">
         <v>106813</v>
@@ -7879,7 +8099,7 @@
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P62" t="inlineStr">
@@ -7888,10 +8108,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>503271</v>
+        <v>503371</v>
       </c>
       <c r="R62" t="n">
-        <v>6610184</v>
+        <v>6610163</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7928,7 +8148,7 @@
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>Ca 15 cm dbh och över 18 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Ca 15 till 30 cm dbh och över 10 m höga. Med askskottsjuka men levande. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7954,13 +8174,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820980</t>
+          <t>https://artportalen.se/Sighting/112820952</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>112820982</v>
+        <v>112820953</v>
       </c>
       <c r="B63" t="n">
         <v>106813</v>
@@ -7990,7 +8210,7 @@
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>25</t>
         </is>
       </c>
       <c r="P63" t="inlineStr">
@@ -7999,10 +8219,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>503266</v>
+        <v>503365</v>
       </c>
       <c r="R63" t="n">
-        <v>6610189</v>
+        <v>6610155</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -8039,7 +8259,7 @@
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>Ca 15 cm dbh och över 15 m hög. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.3 till 1 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -8065,13 +8285,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820982</t>
+          <t>https://artportalen.se/Sighting/112820953</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>112820983</v>
+        <v>112820954</v>
       </c>
       <c r="B64" t="n">
         <v>106813</v>
@@ -8101,7 +8321,7 @@
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P64" t="inlineStr">
@@ -8110,10 +8330,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>503253</v>
+        <v>503343</v>
       </c>
       <c r="R64" t="n">
-        <v>6610191</v>
+        <v>6610144</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -8150,7 +8370,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>Ca 25 cm dbh och över 18 m hög. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Ca 10 till 20 cm dbh och över 10 m höga. Ganska friska fortfarande. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -8176,13 +8396,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820983</t>
+          <t>https://artportalen.se/Sighting/112820954</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>112820985</v>
+        <v>112820957</v>
       </c>
       <c r="B65" t="n">
         <v>106813</v>
@@ -8212,7 +8432,7 @@
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P65" t="inlineStr">
@@ -8221,10 +8441,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>503256</v>
+        <v>503313</v>
       </c>
       <c r="R65" t="n">
-        <v>6610182</v>
+        <v>6610137</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -8261,7 +8481,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Från 0.1 till 0.3 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Ca 4 m hög. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8287,13 +8507,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820985</t>
+          <t>https://artportalen.se/Sighting/112820957</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>112820987</v>
+        <v>112820958</v>
       </c>
       <c r="B66" t="n">
         <v>106813</v>
@@ -8323,7 +8543,7 @@
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
@@ -8332,10 +8552,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>503296</v>
+        <v>503298</v>
       </c>
       <c r="R66" t="n">
-        <v>6610165</v>
+        <v>6610146</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -8372,7 +8592,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>Från 0.3 till 1 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+          <t>Från 0.1 till 0.5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8398,33 +8618,33 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820987</t>
+          <t>https://artportalen.se/Sighting/112820958</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>112820906</v>
+        <v>112820964</v>
       </c>
       <c r="B67" t="n">
-        <v>104628</v>
+        <v>106813</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
@@ -8434,7 +8654,7 @@
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>11</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
@@ -8443,10 +8663,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>503288</v>
+        <v>503285</v>
       </c>
       <c r="R67" t="n">
-        <v>6610263</v>
+        <v>6610146</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -8481,6 +8701,11 @@
           <t>2023-07-18</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Från ca 8 till 30 cm dbh och från ca 15 till 20 m höga. Några döende av askskottsjuka andra tillsynes helt friska. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -8504,33 +8729,33 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820906</t>
+          <t>https://artportalen.se/Sighting/112820964</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>112820921</v>
+        <v>112820965</v>
       </c>
       <c r="B68" t="n">
-        <v>104628</v>
+        <v>106813</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
@@ -8540,7 +8765,7 @@
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
@@ -8549,10 +8774,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>503221</v>
+        <v>503282</v>
       </c>
       <c r="R68" t="n">
-        <v>6610243</v>
+        <v>6610142</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8587,6 +8812,11 @@
           <t>2023-07-18</t>
         </is>
       </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 0.5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
       <c r="AD68" t="b">
         <v>0</v>
       </c>
@@ -8610,33 +8840,33 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820921</t>
+          <t>https://artportalen.se/Sighting/112820965</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>112820922</v>
+        <v>112820967</v>
       </c>
       <c r="B69" t="n">
-        <v>104628</v>
+        <v>106813</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
@@ -8655,10 +8885,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>503228</v>
+        <v>503280</v>
       </c>
       <c r="R69" t="n">
-        <v>6610241</v>
+        <v>6610159</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8693,6 +8923,11 @@
           <t>2023-07-18</t>
         </is>
       </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ca 5 dm dbh. Ca 20 m hög. Spår av askskottsjuka. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -8716,33 +8951,33 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820922</t>
+          <t>https://artportalen.se/Sighting/112820967</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>112820923</v>
+        <v>112820969</v>
       </c>
       <c r="B70" t="n">
-        <v>104628</v>
+        <v>106813</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -8752,7 +8987,7 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
@@ -8761,10 +8996,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>503237</v>
+        <v>503262</v>
       </c>
       <c r="R70" t="n">
-        <v>6610228</v>
+        <v>6610165</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8799,6 +9034,11 @@
           <t>2023-07-18</t>
         </is>
       </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 0.5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -8822,33 +9062,33 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820923</t>
+          <t>https://artportalen.se/Sighting/112820969</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>112820927</v>
+        <v>112820975</v>
       </c>
       <c r="B71" t="n">
-        <v>104628</v>
+        <v>106813</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
@@ -8858,7 +9098,7 @@
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>100</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
@@ -8867,10 +9107,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>503229</v>
+        <v>503254</v>
       </c>
       <c r="R71" t="n">
-        <v>6610213</v>
+        <v>6610139</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8905,6 +9145,11 @@
           <t>2023-07-18</t>
         </is>
       </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 0.5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8928,33 +9173,33 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820927</t>
+          <t>https://artportalen.se/Sighting/112820975</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>112820943</v>
+        <v>112820979</v>
       </c>
       <c r="B72" t="n">
-        <v>104628</v>
+        <v>106813</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
@@ -8964,7 +9209,7 @@
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P72" t="inlineStr">
@@ -8973,10 +9218,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>503341</v>
+        <v>503243</v>
       </c>
       <c r="R72" t="n">
-        <v>6610198</v>
+        <v>6610159</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -9011,6 +9256,11 @@
           <t>2023-07-18</t>
         </is>
       </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 0.5 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
       <c r="AD72" t="b">
         <v>0</v>
       </c>
@@ -9034,33 +9284,33 @@
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820943</t>
+          <t>https://artportalen.se/Sighting/112820979</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>112820945</v>
+        <v>112820980</v>
       </c>
       <c r="B73" t="n">
-        <v>104628</v>
+        <v>106813</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
@@ -9070,7 +9320,7 @@
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -9079,10 +9329,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>503365</v>
+        <v>503271</v>
       </c>
       <c r="R73" t="n">
-        <v>6610181</v>
+        <v>6610184</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -9117,6 +9367,11 @@
           <t>2023-07-18</t>
         </is>
       </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ca 15 cm dbh och över 18 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
       <c r="AD73" t="b">
         <v>0</v>
       </c>
@@ -9140,33 +9395,33 @@
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820945</t>
+          <t>https://artportalen.se/Sighting/112820980</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>112820951</v>
+        <v>112820982</v>
       </c>
       <c r="B74" t="n">
-        <v>104628</v>
+        <v>106813</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
@@ -9185,10 +9440,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>503377</v>
+        <v>503266</v>
       </c>
       <c r="R74" t="n">
-        <v>6610162</v>
+        <v>6610189</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -9225,7 +9480,7 @@
       </c>
       <c r="AC74" t="inlineStr">
         <is>
-          <t>Från 0.1 till 0.5 m höga.</t>
+          <t>Ca 15 cm dbh och över 15 m hög. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9251,33 +9506,33 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820951</t>
+          <t>https://artportalen.se/Sighting/112820982</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>112820955</v>
+        <v>112820983</v>
       </c>
       <c r="B75" t="n">
-        <v>104628</v>
+        <v>106813</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -9287,7 +9542,7 @@
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -9296,10 +9551,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>503329</v>
+        <v>503253</v>
       </c>
       <c r="R75" t="n">
-        <v>6610130</v>
+        <v>6610191</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -9334,6 +9589,11 @@
           <t>2023-07-18</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ca 25 cm dbh och över 18 m hög. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -9357,33 +9617,33 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820955</t>
+          <t>https://artportalen.se/Sighting/112820983</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>112820956</v>
+        <v>112820985</v>
       </c>
       <c r="B76" t="n">
-        <v>104628</v>
+        <v>106813</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -9393,7 +9653,7 @@
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>10</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -9402,10 +9662,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>503324</v>
+        <v>503256</v>
       </c>
       <c r="R76" t="n">
-        <v>6610131</v>
+        <v>6610182</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -9440,6 +9700,11 @@
           <t>2023-07-18</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Från 0.1 till 0.3 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -9463,33 +9728,33 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820956</t>
+          <t>https://artportalen.se/Sighting/112820985</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>112820962</v>
+        <v>112820987</v>
       </c>
       <c r="B77" t="n">
-        <v>104628</v>
+        <v>106813</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>222412</v>
+        <v>220785</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -9499,7 +9764,7 @@
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -9508,10 +9773,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>503294</v>
+        <v>503296</v>
       </c>
       <c r="R77" t="n">
-        <v>6610143</v>
+        <v>6610165</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9546,6 +9811,11 @@
           <t>2023-07-18</t>
         </is>
       </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Från 0.3 till 1 m höga. Dokumentation av asknätfjärilens värdväxter. Länsstyrelsen i Örebro län.</t>
+        </is>
+      </c>
       <c r="AD77" t="b">
         <v>0</v>
       </c>
@@ -9569,13 +9839,13 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820962</t>
+          <t>https://artportalen.se/Sighting/112820987</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>112820963</v>
+        <v>112820906</v>
       </c>
       <c r="B78" t="n">
         <v>104628</v>
@@ -9614,10 +9884,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>503284</v>
+        <v>503288</v>
       </c>
       <c r="R78" t="n">
-        <v>6610144</v>
+        <v>6610263</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9675,13 +9945,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820963</t>
+          <t>https://artportalen.se/Sighting/112820906</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>112820970</v>
+        <v>112820921</v>
       </c>
       <c r="B79" t="n">
         <v>104628</v>
@@ -9720,10 +9990,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>503263</v>
+        <v>503221</v>
       </c>
       <c r="R79" t="n">
-        <v>6610161</v>
+        <v>6610243</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9781,13 +10051,13 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820970</t>
+          <t>https://artportalen.se/Sighting/112820921</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>112820972</v>
+        <v>112820922</v>
       </c>
       <c r="B80" t="n">
         <v>104628</v>
@@ -9817,7 +10087,7 @@
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P80" t="inlineStr">
@@ -9826,10 +10096,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>503254</v>
+        <v>503228</v>
       </c>
       <c r="R80" t="n">
-        <v>6610141</v>
+        <v>6610241</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9887,13 +10157,13 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820972</t>
+          <t>https://artportalen.se/Sighting/112820922</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>112820977</v>
+        <v>112820923</v>
       </c>
       <c r="B81" t="n">
         <v>104628</v>
@@ -9923,7 +10193,7 @@
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>5</t>
         </is>
       </c>
       <c r="P81" t="inlineStr">
@@ -9932,10 +10202,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>503245</v>
+        <v>503237</v>
       </c>
       <c r="R81" t="n">
-        <v>6610159</v>
+        <v>6610228</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9993,13 +10263,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820977</t>
+          <t>https://artportalen.se/Sighting/112820923</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>112820981</v>
+        <v>112820927</v>
       </c>
       <c r="B82" t="n">
         <v>104628</v>
@@ -10029,7 +10299,7 @@
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>3</t>
         </is>
       </c>
       <c r="P82" t="inlineStr">
@@ -10038,10 +10308,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>503278</v>
+        <v>503229</v>
       </c>
       <c r="R82" t="n">
-        <v>6610179</v>
+        <v>6610213</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -10099,16 +10369,16 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820981</t>
+          <t>https://artportalen.se/Sighting/112820927</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>112820938</v>
+        <v>112820943</v>
       </c>
       <c r="B83" t="n">
-        <v>101326</v>
+        <v>104628</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -10116,34 +10386,38 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>400 m SV Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>503290</v>
+        <v>503341</v>
       </c>
       <c r="R83" t="n">
-        <v>6610251</v>
+        <v>6610198</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -10178,11 +10452,6 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="AC83" t="inlineStr">
-        <is>
-          <t>Vanlig i norra delen av beståndet.</t>
-        </is>
-      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -10206,16 +10475,16 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820938</t>
+          <t>https://artportalen.se/Sighting/112820943</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>112820966</v>
+        <v>112820945</v>
       </c>
       <c r="B84" t="n">
-        <v>101326</v>
+        <v>104628</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -10223,34 +10492,38 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>222498</v>
+        <v>222412</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
-      <c r="I84" t="inlineStr"/>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P84" t="inlineStr">
         <is>
           <t>400 m SV Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>503281</v>
+        <v>503365</v>
       </c>
       <c r="R84" t="n">
-        <v>6610146</v>
+        <v>6610181</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -10308,16 +10581,16 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820966</t>
+          <t>https://artportalen.se/Sighting/112820945</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>112820940</v>
+        <v>112820951</v>
       </c>
       <c r="B85" t="n">
-        <v>101228</v>
+        <v>104628</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -10325,16 +10598,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -10342,17 +10615,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>400 m SV Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>503305</v>
+        <v>503377</v>
       </c>
       <c r="R85" t="n">
-        <v>6610237</v>
+        <v>6610162</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -10389,7 +10666,7 @@
       </c>
       <c r="AC85" t="inlineStr">
         <is>
-          <t>Förekommer åtminstone i norra delen av beståndet.</t>
+          <t>Från 0.1 till 0.5 m höga.</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10415,16 +10692,16 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820940</t>
+          <t>https://artportalen.se/Sighting/112820951</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>112820968</v>
+        <v>112820955</v>
       </c>
       <c r="B86" t="n">
-        <v>101228</v>
+        <v>104628</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -10432,16 +10709,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -10451,27 +10728,19 @@
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J86" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="N86" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>400 m SV Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>503271</v>
+        <v>503329</v>
       </c>
       <c r="R86" t="n">
-        <v>6610165</v>
+        <v>6610130</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -10512,7 +10781,6 @@
       <c r="AE86" t="b">
         <v>0</v>
       </c>
-      <c r="AF86" t="inlineStr"/>
       <c r="AG86" t="b">
         <v>0</v>
       </c>
@@ -10530,16 +10798,16 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820968</t>
+          <t>https://artportalen.se/Sighting/112820955</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>112820978</v>
+        <v>112820956</v>
       </c>
       <c r="B87" t="n">
-        <v>101228</v>
+        <v>104628</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -10547,16 +10815,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>222771</v>
+        <v>222412</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Daphne mezereum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -10564,17 +10832,21 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
           <t>400 m SV Ömanstorp, Vstm</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>503241</v>
+        <v>503324</v>
       </c>
       <c r="R87" t="n">
-        <v>6610157</v>
+        <v>6610131</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10632,39 +10904,43 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820978</t>
+          <t>https://artportalen.se/Sighting/112820956</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>112820928</v>
+        <v>112820962</v>
       </c>
       <c r="B88" t="n">
-        <v>103404</v>
+        <v>104628</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>225046</v>
+        <v>222412</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H88" t="inlineStr"/>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>1</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -10673,10 +10949,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>503234</v>
+        <v>503294</v>
       </c>
       <c r="R88" t="n">
-        <v>6610206</v>
+        <v>6610143</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10711,18 +10987,12 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Kring 1 m höga.</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
       <c r="AE88" t="b">
         <v>0</v>
       </c>
-      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
       </c>
@@ -10740,36 +11010,40 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112820928</t>
+          <t>https://artportalen.se/Sighting/112820962</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>112820986</v>
+        <v>112820963</v>
       </c>
       <c r="B89" t="n">
-        <v>103404</v>
+        <v>104628</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>225046</v>
+        <v>222412</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vanlig skogsalm</t>
+          <t>Tibast</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Ulmus glabra subsp. glabra</t>
-        </is>
-      </c>
-      <c r="H89" t="inlineStr"/>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
       <c r="I89" t="inlineStr">
         <is>
           <t>1</t>
@@ -10781,10 +11055,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>503299</v>
+        <v>503284</v>
       </c>
       <c r="R89" t="n">
-        <v>6610170</v>
+        <v>6610144</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10819,18 +11093,12 @@
           <t>2023-07-18</t>
         </is>
       </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Drygt 1 m hög.</t>
-        </is>
-      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
       <c r="AE89" t="b">
         <v>0</v>
       </c>
-      <c r="AF89" t="inlineStr"/>
       <c r="AG89" t="b">
         <v>0</v>
       </c>
@@ -10847,6 +11115,1179 @@
       </c>
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820963</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>112820970</v>
+      </c>
+      <c r="B90" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>503263</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6610161</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820970</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>112820972</v>
+      </c>
+      <c r="B91" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>503254</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6610141</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820972</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>112820977</v>
+      </c>
+      <c r="B92" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>503245</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6610159</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820977</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>112820981</v>
+      </c>
+      <c r="B93" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>503278</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6610179</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820981</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>112820938</v>
+      </c>
+      <c r="B94" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>503290</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6610251</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Vanlig i norra delen av beståndet.</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820938</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>112820966</v>
+      </c>
+      <c r="B95" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>503281</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6610146</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820966</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>112820940</v>
+      </c>
+      <c r="B96" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>503305</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6610237</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Förekommer åtminstone i norra delen av beståndet.</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820940</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>112820968</v>
+      </c>
+      <c r="B97" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K97" t="inlineStr"/>
+      <c r="L97" t="inlineStr"/>
+      <c r="N97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>503271</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6610165</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF97" t="inlineStr"/>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820968</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>112820978</v>
+      </c>
+      <c r="B98" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>503241</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6610157</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820978</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>112820928</v>
+      </c>
+      <c r="B99" t="n">
+        <v>103404</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>225046</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Vanlig skogsalm</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr"/>
+      <c r="I99" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>503234</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6610206</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Kring 1 m höga.</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF99" t="inlineStr"/>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112820928</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="n">
+        <v>112820986</v>
+      </c>
+      <c r="B100" t="n">
+        <v>103404</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E100" t="n">
+        <v>225046</v>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>Vanlig skogsalm</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>Ulmus glabra subsp. glabra</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr"/>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="P100" t="inlineStr">
+        <is>
+          <t>400 m SV Ömanstorp, Vstm</t>
+        </is>
+      </c>
+      <c r="Q100" t="n">
+        <v>503299</v>
+      </c>
+      <c r="R100" t="n">
+        <v>6610170</v>
+      </c>
+      <c r="S100" t="n">
+        <v>10</v>
+      </c>
+      <c r="T100" t="inlineStr">
+        <is>
+          <t>Örebro</t>
+        </is>
+      </c>
+      <c r="U100" t="inlineStr">
+        <is>
+          <t>Lindesberg</t>
+        </is>
+      </c>
+      <c r="V100" t="inlineStr">
+        <is>
+          <t>Västmanland</t>
+        </is>
+      </c>
+      <c r="W100" t="inlineStr">
+        <is>
+          <t>Linde</t>
+        </is>
+      </c>
+      <c r="Y100" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AA100" t="inlineStr">
+        <is>
+          <t>2023-07-18</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Drygt 1 m hög.</t>
+        </is>
+      </c>
+      <c r="AD100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF100" t="inlineStr"/>
+      <c r="AG100" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT100" t="inlineStr"/>
+      <c r="AW100" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AX100" t="inlineStr">
+        <is>
+          <t>Jesper Hansson</t>
+        </is>
+      </c>
+      <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/112820986</t>
         </is>
@@ -10942,6 +12383,17 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
